--- a/artfynd/A 57537-2024 artfynd.xlsx
+++ b/artfynd/A 57537-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1262,6 +1262,541 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>122773593</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57478</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Slåttmyrtjärnarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>438528</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7009754</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Mattmar</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>122773623</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57478</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Slåttmyrtjärnarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>438448</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7009132</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Mattmar</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>122773621</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57478</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Slåttmyrtjärnarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>438602</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7009616</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Mattmar</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>122773620</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57478</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Slåttmyrtjärnarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>438573</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7009738</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Mattmar</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>122773622</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57478</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Slåttmyrtjärnarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>438560</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7009535</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Mattmar</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 57537-2024 artfynd.xlsx
+++ b/artfynd/A 57537-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1798,6 +1798,220 @@
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>122797615</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57478</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Slåttmyrtjärnarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>438234</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7009293</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Mattmar</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>122797614</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57478</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Slåttmyrtjärnarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>438207</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7009418</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Mattmar</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 57537-2024 artfynd.xlsx
+++ b/artfynd/A 57537-2024 artfynd.xlsx
@@ -1265,7 +1265,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122773593</v>
+        <v>122773622</v>
       </c>
       <c r="B7" t="n">
         <v>57478</v>
@@ -1305,10 +1305,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>438528</v>
+        <v>438560</v>
       </c>
       <c r="R7" t="n">
-        <v>7009754</v>
+        <v>7009535</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1345,7 +1345,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1479,7 +1479,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122773621</v>
+        <v>122773620</v>
       </c>
       <c r="B9" t="n">
         <v>57478</v>
@@ -1519,10 +1519,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>438602</v>
+        <v>438573</v>
       </c>
       <c r="R9" t="n">
-        <v>7009616</v>
+        <v>7009738</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1559,7 +1559,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1586,7 +1586,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122773620</v>
+        <v>122773621</v>
       </c>
       <c r="B10" t="n">
         <v>57478</v>
@@ -1626,10 +1626,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>438573</v>
+        <v>438602</v>
       </c>
       <c r="R10" t="n">
-        <v>7009738</v>
+        <v>7009616</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1666,7 +1666,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1693,7 +1693,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122773622</v>
+        <v>122773593</v>
       </c>
       <c r="B11" t="n">
         <v>57478</v>
@@ -1733,10 +1733,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>438560</v>
+        <v>438528</v>
       </c>
       <c r="R11" t="n">
-        <v>7009535</v>
+        <v>7009754</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1800,7 +1800,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122797615</v>
+        <v>122797614</v>
       </c>
       <c r="B12" t="n">
         <v>57478</v>
@@ -1840,10 +1840,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>438234</v>
+        <v>438207</v>
       </c>
       <c r="R12" t="n">
-        <v>7009293</v>
+        <v>7009418</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1907,7 +1907,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122797614</v>
+        <v>122797615</v>
       </c>
       <c r="B13" t="n">
         <v>57478</v>
@@ -1947,10 +1947,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>438207</v>
+        <v>438234</v>
       </c>
       <c r="R13" t="n">
-        <v>7009418</v>
+        <v>7009293</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 57537-2024 artfynd.xlsx
+++ b/artfynd/A 57537-2024 artfynd.xlsx
@@ -1265,7 +1265,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122773622</v>
+        <v>122773623</v>
       </c>
       <c r="B7" t="n">
         <v>57478</v>
@@ -1305,10 +1305,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>438560</v>
+        <v>438448</v>
       </c>
       <c r="R7" t="n">
-        <v>7009535</v>
+        <v>7009132</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1345,7 +1345,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1372,7 +1372,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122773623</v>
+        <v>122773620</v>
       </c>
       <c r="B8" t="n">
         <v>57478</v>
@@ -1412,10 +1412,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>438448</v>
+        <v>438573</v>
       </c>
       <c r="R8" t="n">
-        <v>7009132</v>
+        <v>7009738</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1479,7 +1479,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122773620</v>
+        <v>122773621</v>
       </c>
       <c r="B9" t="n">
         <v>57478</v>
@@ -1519,10 +1519,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>438573</v>
+        <v>438602</v>
       </c>
       <c r="R9" t="n">
-        <v>7009738</v>
+        <v>7009616</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1559,7 +1559,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1586,7 +1586,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122773621</v>
+        <v>122773622</v>
       </c>
       <c r="B10" t="n">
         <v>57478</v>
@@ -1626,10 +1626,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>438602</v>
+        <v>438560</v>
       </c>
       <c r="R10" t="n">
-        <v>7009616</v>
+        <v>7009535</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1666,7 +1666,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 57537-2024 artfynd.xlsx
+++ b/artfynd/A 57537-2024 artfynd.xlsx
@@ -1265,7 +1265,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122773623</v>
+        <v>122773620</v>
       </c>
       <c r="B7" t="n">
         <v>57478</v>
@@ -1305,10 +1305,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>438448</v>
+        <v>438573</v>
       </c>
       <c r="R7" t="n">
-        <v>7009132</v>
+        <v>7009738</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1345,7 +1345,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1372,7 +1372,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122773620</v>
+        <v>122773622</v>
       </c>
       <c r="B8" t="n">
         <v>57478</v>
@@ -1412,10 +1412,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>438573</v>
+        <v>438560</v>
       </c>
       <c r="R8" t="n">
-        <v>7009738</v>
+        <v>7009535</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1479,7 +1479,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122773621</v>
+        <v>122773623</v>
       </c>
       <c r="B9" t="n">
         <v>57478</v>
@@ -1519,10 +1519,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>438602</v>
+        <v>438448</v>
       </c>
       <c r="R9" t="n">
-        <v>7009616</v>
+        <v>7009132</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1559,7 +1559,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1586,7 +1586,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122773622</v>
+        <v>122773621</v>
       </c>
       <c r="B10" t="n">
         <v>57478</v>
@@ -1626,10 +1626,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>438560</v>
+        <v>438602</v>
       </c>
       <c r="R10" t="n">
-        <v>7009535</v>
+        <v>7009616</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1666,7 +1666,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1800,7 +1800,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122797614</v>
+        <v>122797615</v>
       </c>
       <c r="B12" t="n">
         <v>57478</v>
@@ -1840,10 +1840,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>438207</v>
+        <v>438234</v>
       </c>
       <c r="R12" t="n">
-        <v>7009418</v>
+        <v>7009293</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1907,7 +1907,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122797615</v>
+        <v>122797614</v>
       </c>
       <c r="B13" t="n">
         <v>57478</v>
@@ -1947,10 +1947,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>438234</v>
+        <v>438207</v>
       </c>
       <c r="R13" t="n">
-        <v>7009293</v>
+        <v>7009418</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 57537-2024 artfynd.xlsx
+++ b/artfynd/A 57537-2024 artfynd.xlsx
@@ -1265,7 +1265,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122773620</v>
+        <v>122773622</v>
       </c>
       <c r="B7" t="n">
         <v>57478</v>
@@ -1305,10 +1305,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>438573</v>
+        <v>438560</v>
       </c>
       <c r="R7" t="n">
-        <v>7009738</v>
+        <v>7009535</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1345,7 +1345,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1372,7 +1372,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122773622</v>
+        <v>122773620</v>
       </c>
       <c r="B8" t="n">
         <v>57478</v>
@@ -1412,10 +1412,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>438560</v>
+        <v>438573</v>
       </c>
       <c r="R8" t="n">
-        <v>7009535</v>
+        <v>7009738</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1479,7 +1479,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122773623</v>
+        <v>122773593</v>
       </c>
       <c r="B9" t="n">
         <v>57478</v>
@@ -1519,10 +1519,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>438448</v>
+        <v>438528</v>
       </c>
       <c r="R9" t="n">
-        <v>7009132</v>
+        <v>7009754</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1586,7 +1586,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122773621</v>
+        <v>122773623</v>
       </c>
       <c r="B10" t="n">
         <v>57478</v>
@@ -1626,10 +1626,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>438602</v>
+        <v>438448</v>
       </c>
       <c r="R10" t="n">
-        <v>7009616</v>
+        <v>7009132</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1666,7 +1666,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1693,7 +1693,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122773593</v>
+        <v>122773621</v>
       </c>
       <c r="B11" t="n">
         <v>57478</v>
@@ -1733,10 +1733,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>438528</v>
+        <v>438602</v>
       </c>
       <c r="R11" t="n">
-        <v>7009754</v>
+        <v>7009616</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 57537-2024 artfynd.xlsx
+++ b/artfynd/A 57537-2024 artfynd.xlsx
@@ -1265,7 +1265,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122773622</v>
+        <v>122773623</v>
       </c>
       <c r="B7" t="n">
         <v>57478</v>
@@ -1305,10 +1305,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>438560</v>
+        <v>438448</v>
       </c>
       <c r="R7" t="n">
-        <v>7009535</v>
+        <v>7009132</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1345,7 +1345,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1372,7 +1372,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122773620</v>
+        <v>122773622</v>
       </c>
       <c r="B8" t="n">
         <v>57478</v>
@@ -1412,10 +1412,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>438573</v>
+        <v>438560</v>
       </c>
       <c r="R8" t="n">
-        <v>7009738</v>
+        <v>7009535</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1586,7 +1586,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122773623</v>
+        <v>122773620</v>
       </c>
       <c r="B10" t="n">
         <v>57478</v>
@@ -1626,10 +1626,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>438448</v>
+        <v>438573</v>
       </c>
       <c r="R10" t="n">
-        <v>7009132</v>
+        <v>7009738</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1666,7 +1666,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1800,7 +1800,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122797615</v>
+        <v>122797614</v>
       </c>
       <c r="B12" t="n">
         <v>57478</v>
@@ -1840,10 +1840,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>438234</v>
+        <v>438207</v>
       </c>
       <c r="R12" t="n">
-        <v>7009293</v>
+        <v>7009418</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1907,7 +1907,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122797614</v>
+        <v>122797615</v>
       </c>
       <c r="B13" t="n">
         <v>57478</v>
@@ -1947,10 +1947,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>438207</v>
+        <v>438234</v>
       </c>
       <c r="R13" t="n">
-        <v>7009418</v>
+        <v>7009293</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 57537-2024 artfynd.xlsx
+++ b/artfynd/A 57537-2024 artfynd.xlsx
@@ -1265,7 +1265,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122773623</v>
+        <v>122773622</v>
       </c>
       <c r="B7" t="n">
         <v>57478</v>
@@ -1305,10 +1305,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>438448</v>
+        <v>438560</v>
       </c>
       <c r="R7" t="n">
-        <v>7009132</v>
+        <v>7009535</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1345,7 +1345,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1372,7 +1372,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122773622</v>
+        <v>122773620</v>
       </c>
       <c r="B8" t="n">
         <v>57478</v>
@@ -1412,10 +1412,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>438560</v>
+        <v>438573</v>
       </c>
       <c r="R8" t="n">
-        <v>7009535</v>
+        <v>7009738</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1586,7 +1586,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122773620</v>
+        <v>122773621</v>
       </c>
       <c r="B10" t="n">
         <v>57478</v>
@@ -1626,10 +1626,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>438573</v>
+        <v>438602</v>
       </c>
       <c r="R10" t="n">
-        <v>7009738</v>
+        <v>7009616</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1666,7 +1666,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1693,7 +1693,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122773621</v>
+        <v>122773623</v>
       </c>
       <c r="B11" t="n">
         <v>57478</v>
@@ -1733,10 +1733,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>438602</v>
+        <v>438448</v>
       </c>
       <c r="R11" t="n">
-        <v>7009616</v>
+        <v>7009132</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 57537-2024 artfynd.xlsx
+++ b/artfynd/A 57537-2024 artfynd.xlsx
@@ -1265,7 +1265,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122773622</v>
+        <v>122773621</v>
       </c>
       <c r="B7" t="n">
         <v>57478</v>
@@ -1305,10 +1305,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>438560</v>
+        <v>438602</v>
       </c>
       <c r="R7" t="n">
-        <v>7009535</v>
+        <v>7009616</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1345,7 +1345,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1372,7 +1372,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122773620</v>
+        <v>122773593</v>
       </c>
       <c r="B8" t="n">
         <v>57478</v>
@@ -1412,10 +1412,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>438573</v>
+        <v>438528</v>
       </c>
       <c r="R8" t="n">
-        <v>7009738</v>
+        <v>7009754</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1479,7 +1479,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122773593</v>
+        <v>122773622</v>
       </c>
       <c r="B9" t="n">
         <v>57478</v>
@@ -1519,10 +1519,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>438528</v>
+        <v>438560</v>
       </c>
       <c r="R9" t="n">
-        <v>7009754</v>
+        <v>7009535</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1559,7 +1559,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1586,7 +1586,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122773621</v>
+        <v>122773620</v>
       </c>
       <c r="B10" t="n">
         <v>57478</v>
@@ -1626,10 +1626,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>438602</v>
+        <v>438573</v>
       </c>
       <c r="R10" t="n">
-        <v>7009616</v>
+        <v>7009738</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1666,7 +1666,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1800,7 +1800,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122797614</v>
+        <v>122797615</v>
       </c>
       <c r="B12" t="n">
         <v>57478</v>
@@ -1840,10 +1840,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>438207</v>
+        <v>438234</v>
       </c>
       <c r="R12" t="n">
-        <v>7009418</v>
+        <v>7009293</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1907,7 +1907,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122797615</v>
+        <v>122797614</v>
       </c>
       <c r="B13" t="n">
         <v>57478</v>
@@ -1947,10 +1947,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>438234</v>
+        <v>438207</v>
       </c>
       <c r="R13" t="n">
-        <v>7009293</v>
+        <v>7009418</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 57537-2024 artfynd.xlsx
+++ b/artfynd/A 57537-2024 artfynd.xlsx
@@ -1265,7 +1265,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122773621</v>
+        <v>122773622</v>
       </c>
       <c r="B7" t="n">
         <v>57478</v>
@@ -1305,10 +1305,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>438602</v>
+        <v>438560</v>
       </c>
       <c r="R7" t="n">
-        <v>7009616</v>
+        <v>7009535</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1345,7 +1345,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1372,7 +1372,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122773593</v>
+        <v>122773620</v>
       </c>
       <c r="B8" t="n">
         <v>57478</v>
@@ -1412,10 +1412,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>438528</v>
+        <v>438573</v>
       </c>
       <c r="R8" t="n">
-        <v>7009754</v>
+        <v>7009738</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1479,7 +1479,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122773622</v>
+        <v>122773593</v>
       </c>
       <c r="B9" t="n">
         <v>57478</v>
@@ -1519,10 +1519,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>438560</v>
+        <v>438528</v>
       </c>
       <c r="R9" t="n">
-        <v>7009535</v>
+        <v>7009754</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1559,7 +1559,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1586,7 +1586,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122773620</v>
+        <v>122773621</v>
       </c>
       <c r="B10" t="n">
         <v>57478</v>
@@ -1626,10 +1626,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>438573</v>
+        <v>438602</v>
       </c>
       <c r="R10" t="n">
-        <v>7009738</v>
+        <v>7009616</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1666,7 +1666,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1800,7 +1800,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122797615</v>
+        <v>122797614</v>
       </c>
       <c r="B12" t="n">
         <v>57478</v>
@@ -1840,10 +1840,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>438234</v>
+        <v>438207</v>
       </c>
       <c r="R12" t="n">
-        <v>7009293</v>
+        <v>7009418</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1907,7 +1907,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122797614</v>
+        <v>122797615</v>
       </c>
       <c r="B13" t="n">
         <v>57478</v>
@@ -1947,10 +1947,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>438207</v>
+        <v>438234</v>
       </c>
       <c r="R13" t="n">
-        <v>7009418</v>
+        <v>7009293</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 57537-2024 artfynd.xlsx
+++ b/artfynd/A 57537-2024 artfynd.xlsx
@@ -1265,7 +1265,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122773622</v>
+        <v>122773620</v>
       </c>
       <c r="B7" t="n">
         <v>57478</v>
@@ -1305,10 +1305,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>438560</v>
+        <v>438573</v>
       </c>
       <c r="R7" t="n">
-        <v>7009535</v>
+        <v>7009738</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1345,7 +1345,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1372,7 +1372,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122773620</v>
+        <v>122773622</v>
       </c>
       <c r="B8" t="n">
         <v>57478</v>
@@ -1412,10 +1412,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>438573</v>
+        <v>438560</v>
       </c>
       <c r="R8" t="n">
-        <v>7009738</v>
+        <v>7009535</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1800,7 +1800,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122797614</v>
+        <v>122797615</v>
       </c>
       <c r="B12" t="n">
         <v>57478</v>
@@ -1840,10 +1840,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>438207</v>
+        <v>438234</v>
       </c>
       <c r="R12" t="n">
-        <v>7009418</v>
+        <v>7009293</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1907,7 +1907,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122797615</v>
+        <v>122797614</v>
       </c>
       <c r="B13" t="n">
         <v>57478</v>
@@ -1947,10 +1947,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>438234</v>
+        <v>438207</v>
       </c>
       <c r="R13" t="n">
-        <v>7009293</v>
+        <v>7009418</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 57537-2024 artfynd.xlsx
+++ b/artfynd/A 57537-2024 artfynd.xlsx
@@ -1265,10 +1265,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122773620</v>
+        <v>122773623</v>
       </c>
       <c r="B7" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1305,10 +1305,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>438573</v>
+        <v>438448</v>
       </c>
       <c r="R7" t="n">
-        <v>7009738</v>
+        <v>7009132</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1345,7 +1345,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1375,7 +1375,7 @@
         <v>122773622</v>
       </c>
       <c r="B8" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1482,7 +1482,7 @@
         <v>122773593</v>
       </c>
       <c r="B9" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1586,10 +1586,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122773621</v>
+        <v>122773620</v>
       </c>
       <c r="B10" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1626,10 +1626,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>438602</v>
+        <v>438573</v>
       </c>
       <c r="R10" t="n">
-        <v>7009616</v>
+        <v>7009738</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1666,7 +1666,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1693,10 +1693,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122773623</v>
+        <v>122773621</v>
       </c>
       <c r="B11" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1733,10 +1733,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>438448</v>
+        <v>438602</v>
       </c>
       <c r="R11" t="n">
-        <v>7009132</v>
+        <v>7009616</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1803,7 +1803,7 @@
         <v>122797615</v>
       </c>
       <c r="B12" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1910,7 +1910,7 @@
         <v>122797614</v>
       </c>
       <c r="B13" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>

--- a/artfynd/A 57537-2024 artfynd.xlsx
+++ b/artfynd/A 57537-2024 artfynd.xlsx
@@ -1265,7 +1265,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122773623</v>
+        <v>122773593</v>
       </c>
       <c r="B7" t="n">
         <v>57481</v>
@@ -1305,10 +1305,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>438448</v>
+        <v>438528</v>
       </c>
       <c r="R7" t="n">
-        <v>7009132</v>
+        <v>7009754</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1372,7 +1372,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122773622</v>
+        <v>122773623</v>
       </c>
       <c r="B8" t="n">
         <v>57481</v>
@@ -1412,10 +1412,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>438560</v>
+        <v>438448</v>
       </c>
       <c r="R8" t="n">
-        <v>7009535</v>
+        <v>7009132</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1479,7 +1479,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122773593</v>
+        <v>122773620</v>
       </c>
       <c r="B9" t="n">
         <v>57481</v>
@@ -1519,10 +1519,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>438528</v>
+        <v>438573</v>
       </c>
       <c r="R9" t="n">
-        <v>7009754</v>
+        <v>7009738</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1559,7 +1559,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1586,7 +1586,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122773620</v>
+        <v>122773621</v>
       </c>
       <c r="B10" t="n">
         <v>57481</v>
@@ -1626,10 +1626,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>438573</v>
+        <v>438602</v>
       </c>
       <c r="R10" t="n">
-        <v>7009738</v>
+        <v>7009616</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1666,7 +1666,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1693,7 +1693,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122773621</v>
+        <v>122773622</v>
       </c>
       <c r="B11" t="n">
         <v>57481</v>
@@ -1733,10 +1733,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>438602</v>
+        <v>438560</v>
       </c>
       <c r="R11" t="n">
-        <v>7009616</v>
+        <v>7009535</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1800,7 +1800,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122797615</v>
+        <v>122797614</v>
       </c>
       <c r="B12" t="n">
         <v>57481</v>
@@ -1840,10 +1840,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>438234</v>
+        <v>438207</v>
       </c>
       <c r="R12" t="n">
-        <v>7009293</v>
+        <v>7009418</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1907,7 +1907,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122797614</v>
+        <v>122797615</v>
       </c>
       <c r="B13" t="n">
         <v>57481</v>
@@ -1947,10 +1947,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>438207</v>
+        <v>438234</v>
       </c>
       <c r="R13" t="n">
-        <v>7009418</v>
+        <v>7009293</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 57537-2024 artfynd.xlsx
+++ b/artfynd/A 57537-2024 artfynd.xlsx
@@ -1265,7 +1265,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122773593</v>
+        <v>122773623</v>
       </c>
       <c r="B7" t="n">
         <v>57481</v>
@@ -1305,10 +1305,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>438528</v>
+        <v>438448</v>
       </c>
       <c r="R7" t="n">
-        <v>7009754</v>
+        <v>7009132</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1372,7 +1372,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122773623</v>
+        <v>122773621</v>
       </c>
       <c r="B8" t="n">
         <v>57481</v>
@@ -1412,10 +1412,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>438448</v>
+        <v>438602</v>
       </c>
       <c r="R8" t="n">
-        <v>7009132</v>
+        <v>7009616</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1586,7 +1586,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122773621</v>
+        <v>122773622</v>
       </c>
       <c r="B10" t="n">
         <v>57481</v>
@@ -1626,10 +1626,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>438602</v>
+        <v>438560</v>
       </c>
       <c r="R10" t="n">
-        <v>7009616</v>
+        <v>7009535</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1666,7 +1666,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1693,7 +1693,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122773622</v>
+        <v>122773593</v>
       </c>
       <c r="B11" t="n">
         <v>57481</v>
@@ -1733,10 +1733,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>438560</v>
+        <v>438528</v>
       </c>
       <c r="R11" t="n">
-        <v>7009535</v>
+        <v>7009754</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1800,7 +1800,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122797614</v>
+        <v>122797615</v>
       </c>
       <c r="B12" t="n">
         <v>57481</v>
@@ -1840,10 +1840,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>438207</v>
+        <v>438234</v>
       </c>
       <c r="R12" t="n">
-        <v>7009418</v>
+        <v>7009293</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1907,7 +1907,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122797615</v>
+        <v>122797614</v>
       </c>
       <c r="B13" t="n">
         <v>57481</v>
@@ -1947,10 +1947,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>438234</v>
+        <v>438207</v>
       </c>
       <c r="R13" t="n">
-        <v>7009293</v>
+        <v>7009418</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 57537-2024 artfynd.xlsx
+++ b/artfynd/A 57537-2024 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>89600480</v>
+        <v>89600501</v>
       </c>
       <c r="B2" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>438498.0747472956</v>
+        <v>438333</v>
       </c>
       <c r="R2" t="n">
-        <v>7009646.875433688</v>
+        <v>7009221</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,21 +743,11 @@
           <t>2020-09-24</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-09-25</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -771,11 +756,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>En hane</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -796,37 +776,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>89600476</v>
+        <v>89600498</v>
       </c>
       <c r="B3" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -836,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>438329.967187647</v>
+        <v>438334</v>
       </c>
       <c r="R3" t="n">
-        <v>7009220.039179727</v>
+        <v>7009218</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,24 +844,9 @@
           <t>2020-09-24</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2020-09-25</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,15 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>89600483</v>
+        <v>89600476</v>
       </c>
       <c r="B4" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -933,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -957,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>438333.9724820413</v>
+        <v>438330</v>
       </c>
       <c r="R4" t="n">
-        <v>7009216.803667132</v>
+        <v>7009220</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -990,19 +945,14 @@
           <t>2020-09-24</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2020-09-25</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1033,15 +983,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>89600501</v>
+        <v>89600480</v>
       </c>
       <c r="B5" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1049,21 +994,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1073,10 +1018,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>438333.1465810707</v>
+        <v>438498</v>
       </c>
       <c r="R5" t="n">
-        <v>7009220.88099837</v>
+        <v>7009647</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1106,21 +1051,11 @@
           <t>2020-09-24</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2020-09-25</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1129,6 +1064,11 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>En hane</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1149,15 +1089,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>89600498</v>
+        <v>122773593</v>
       </c>
       <c r="B6" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1165,34 +1100,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Baksjöhallen, Jmt</t>
+          <t>Slåttmyrtjärnarna, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>438333.9983392665</v>
+        <v>438528</v>
       </c>
       <c r="R6" t="n">
-        <v>7009218.157024155</v>
+        <v>7009754</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1219,22 +1154,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2020-09-24</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2020-09-25</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1249,31 +1179,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122773623</v>
+        <v>122773620</v>
       </c>
       <c r="B7" t="n">
-        <v>57481</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1305,10 +1226,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>438448</v>
+        <v>438573</v>
       </c>
       <c r="R7" t="n">
-        <v>7009132</v>
+        <v>7009738</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1345,7 +1266,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1375,12 +1296,7 @@
         <v>122773621</v>
       </c>
       <c r="B8" t="n">
-        <v>57481</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1479,15 +1395,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122773620</v>
+        <v>122773622</v>
       </c>
       <c r="B9" t="n">
-        <v>57481</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1519,10 +1430,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>438573</v>
+        <v>438560</v>
       </c>
       <c r="R9" t="n">
-        <v>7009738</v>
+        <v>7009535</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1559,7 +1470,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1586,15 +1497,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122773622</v>
+        <v>122773623</v>
       </c>
       <c r="B10" t="n">
-        <v>57481</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1626,10 +1532,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>438560</v>
+        <v>438448</v>
       </c>
       <c r="R10" t="n">
-        <v>7009535</v>
+        <v>7009132</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1666,7 +1572,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1693,15 +1599,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122773593</v>
+        <v>122797610</v>
       </c>
       <c r="B11" t="n">
-        <v>57481</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1733,10 +1634,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>438528</v>
+        <v>438597</v>
       </c>
       <c r="R11" t="n">
-        <v>7009754</v>
+        <v>7009430</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1763,17 +1664,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1800,15 +1701,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122797615</v>
+        <v>122797614</v>
       </c>
       <c r="B12" t="n">
-        <v>57481</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1840,10 +1736,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>438234</v>
+        <v>438207</v>
       </c>
       <c r="R12" t="n">
-        <v>7009293</v>
+        <v>7009418</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1907,15 +1803,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122797614</v>
+        <v>122797615</v>
       </c>
       <c r="B13" t="n">
-        <v>57481</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1947,10 +1838,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>438207</v>
+        <v>438234</v>
       </c>
       <c r="R13" t="n">
-        <v>7009418</v>
+        <v>7009293</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 57537-2024 artfynd.xlsx
+++ b/artfynd/A 57537-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89600501</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89600498</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -980,6 +995,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89600476</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1086,6 +1106,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89600480</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1188,6 +1213,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122773593</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1290,6 +1320,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122773620</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1392,6 +1427,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122773621</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1494,6 +1534,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122773622</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1596,6 +1641,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122773623</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1698,6 +1748,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122797610</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1800,6 +1855,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122797614</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1902,8 +1962,27 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122797615</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>